--- a/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/2 Lecture Demos/4 Heated clothes rack in Excel.xlsx
+++ b/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/2 Lecture Demos/4 Heated clothes rack in Excel.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimailderbyac-my.sharepoint.com/personal/tcsr529_derby_ac_uk/Documents/_Teaching/202526/5CM522 - Operational Research/Lectures/Semester 2/Week 1 - Introduction to Simulation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="9" documentId="8_{35BD98EE-DFDB-440E-A305-4E38CC49026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACC3BCEC-0166-47B4-9DBB-67A9C41D8D02}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="18590" yWindow="1010" windowWidth="21600" windowHeight="11000" xr2:uid="{C4FBD617-E120-47C6-809F-240468746785}"/>
